--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-careplan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-careplan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-careplan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-careplan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -380,7 +380,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>CarePlan.meta.versionId</t>
@@ -743,7 +743,7 @@
     <t>CarePlan.status</t>
   </si>
   <si>
-    <t>下書き| アクティブ| 保留中| 取り消された| 完了| エラーで入力| 不明</t>
+    <t>下書き| アクティブ| 保留中| 取り消された| 完了 | エラー入力| 不明</t>
   </si>
   <si>
     <t>計画が実行中か、将来の意図を表しているか、現在歴史的記録であるかを示します。</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-careplan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-careplan.xlsx
@@ -889,10 +889,10 @@
 </t>
   </si>
   <si>
-    <t>一部として作成されたEncounter（診察、受診、入退院など）</t>
-  </si>
-  <si>
-    <t>このCarePlanが作成されたEncounter（診察、受診、入退院など）、またはこの記録の作成に密接に関係するEncounter（診察、受診、入退院など）。</t>
+    <t>一部として作成された受療行動</t>
+  </si>
+  <si>
+    <t>このCarePlanが作成された受療行動、またはこの記録の作成に密接に関係する受療行動。</t>
   </si>
   <si>
     <t>これは通常、イベントが発生したエンカウンター内で行われますが、公式的なエンカウンターの完了前または後でも、エンカウンターの文脈に関連するアクティビティが開始される場合があります。 ケアプランに従って実施されるケアプランアクティビティは、他のエンカウンターの一部として行われる可能性があります。</t>
@@ -1176,7 +1176,7 @@
     <t>CarePlan.activity.outcomeReference</t>
   </si>
   <si>
-    <t>予約、Encounter（診察、受診、入退院など）、手続きなど。</t>
+    <t>予約、受療行動、手続きなど。</t>
   </si>
   <si>
     <t>アクティビティによって生じる結果や行動の詳細。プロシジャー（処置等）、エンカウンター、観察などの「イベント」リソースに参照していることは、アクティビティそのものの結果/成果です。CarePlan.activity.detailを使用するか、CarePlan.activity.reference（「リクエスト」リソースへの参照）を使用してアクティビティを伝えることができます。</t>
@@ -1315,7 +1315,7 @@
     <t>活動の詳細タイプ</t>
   </si>
   <si>
-    <t>計画された活動の詳細な説明；例えば、どのようなラボテスト、どのようなプロシジャー（処置等）、どのようなEncounter（診察、受診、入退院など）か。</t>
+    <t>計画された活動の詳細な説明；例えば、どのようなラボテスト、どのようなプロシジャー（処置等）、どのような受療行動か。</t>
   </si>
   <si>
     <t>特定の製品に関する活動においては、あまり関係がない傾向があります。コードに否定を示すことは避け、代わりに「禁止」としてください。</t>
@@ -1324,7 +1324,7 @@
     <t>Allows matching performed to planned as well as validation against protocols.</t>
   </si>
   <si>
-    <t>活動の種類に関する詳細な説明例：どのような実験、どのプロシジャー（処置等）、どのようなEncounter（診察、受診、入退院など）ですか。</t>
+    <t>活動の種類に関する詳細な説明例：どのような実験、どのプロシジャー（処置等）、どのような受療行動ですか。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
